--- a/AAII_Financials/Quarterly/MSGS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MSGS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>MSGS</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>278700</v>
+      </c>
+      <c r="E8" s="3">
         <v>432200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>403400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>39500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>204000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>424200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>357800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>53300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>227300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>430000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>326900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>43000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>126900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>382700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>353700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>175200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>337800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>289600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>146900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>183000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>57000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>603300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>267600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>292800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>49900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>729400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>517200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>632200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>218100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>153400</v>
+      </c>
+      <c r="E9" s="3">
         <v>324400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>281300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>148700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>249000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>101200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>237700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>207900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>76600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>207700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>193900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>83500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>176500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>165000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>84700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>106000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>39700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>359500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>161300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>197600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>18300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>440100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>310800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>386800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>123900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>418000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E10" s="3">
         <v>107800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>122100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>55300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>141200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>126100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>192300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>119000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>175000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>159800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>91700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>161300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>124600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>62200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>77000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>243800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>106300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>95200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>31600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>289300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>206400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>245400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>94200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-100000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,61 +1358,64 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>8400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9800</v>
       </c>
-      <c r="G14" s="3">
-        <v>2000</v>
-      </c>
       <c r="H14" s="3">
+        <v>700</v>
+      </c>
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-2600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-7600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1418,12 +1438,12 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>102200</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1481,19 +1504,19 @@
         <v>800</v>
       </c>
       <c r="O15" s="3">
+        <v>800</v>
+      </c>
+      <c r="P15" s="3">
         <v>900</v>
-      </c>
-      <c r="P15" s="3">
-        <v>800</v>
       </c>
       <c r="Q15" s="3">
         <v>800</v>
       </c>
       <c r="R15" s="3">
+        <v>800</v>
+      </c>
+      <c r="S15" s="3">
         <v>1000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1200</v>
       </c>
       <c r="T15" s="3">
         <v>1200</v>
@@ -1502,49 +1525,52 @@
         <v>1200</v>
       </c>
       <c r="V15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W15" s="3">
         <v>1400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>1600</v>
       </c>
       <c r="Y15" s="3">
         <v>1600</v>
       </c>
       <c r="Z15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>1700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>17500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>5600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>4900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>4800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>20100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>28900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>30200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>29700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E17" s="3">
         <v>429000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>381200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>66900</v>
       </c>
-      <c r="G17" s="3">
-        <v>226600</v>
-      </c>
       <c r="H17" s="3">
+        <v>227300</v>
+      </c>
+      <c r="I17" s="3">
         <v>391900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>344400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>175000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>350300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>298200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>139200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>301100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>302200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>60000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>151500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>276400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>253700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>167700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>174900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>84400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>697200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>257000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>293000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>109200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>787600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>478700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>553900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>268900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>362100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-22700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I18" s="3">
         <v>32300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>52200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>79700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>81700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>51500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>61400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-34900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-20800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-93900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-59300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-58200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>38500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>78300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-50800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-44100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,62 +1849,63 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1879,450 +1913,465 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>-100</v>
       </c>
       <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>300</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>21500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>22700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-20700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="I21" s="3">
         <v>30900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>79200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>30000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>94200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>53300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-34700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>62600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-33500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-20100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-36900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>40300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-30100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>63500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>78800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>112000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-17000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>4800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5000</v>
       </c>
       <c r="H22" s="3">
         <v>5000</v>
       </c>
       <c r="I22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3">
         <v>5600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3600</v>
-      </c>
-      <c r="V22" s="3">
-        <v>3100</v>
       </c>
       <c r="W22" s="3">
         <v>3100</v>
       </c>
       <c r="X22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>2900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>71900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>94800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-39000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>58900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-38100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-24000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-98000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-59700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-60600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>45400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>76600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-33400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-51900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6700</v>
+        <v>5400</v>
       </c>
       <c r="E24" s="3">
         <v>6700</v>
       </c>
       <c r="F24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G24" s="3">
         <v>-8600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-25300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>36900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>34000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-15100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-20500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-21200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-73100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>20600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-19500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-12600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11300</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>700</v>
       </c>
       <c r="AH24" s="3">
         <v>700</v>
       </c>
       <c r="AI24" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>51800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>49200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-41100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-118600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-40200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>34200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>76000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-50500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>52400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>49600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-116300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>27400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-39600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>35300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>81600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-32200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2781,14 +2842,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2800,34 +2861,37 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-66100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-123000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>97300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-40200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>57100</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,62 +3095,65 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5300</v>
       </c>
-      <c r="G32" s="3">
-        <v>1100</v>
-      </c>
       <c r="H32" s="3">
+        <v>400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3091,147 +3161,153 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>100</v>
       </c>
       <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>52400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>49600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-182400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-95600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>95400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-79800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>35300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>81600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-32200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>52400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>49600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-182400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-95600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>95400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-79800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>35300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>81600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-32200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>164500</v>
+      </c>
+      <c r="E41" s="3">
         <v>107000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>81300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>144600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>91000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>49200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>33600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>64900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>69100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>70800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>77900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1006300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1000100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>952200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1153100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1227900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1068900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3784,139 +3874,145 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
+      <c r="Z42" s="3">
+        <v>0</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="3">
         <v>331000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>113000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>104600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>108400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>110900</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E43" s="3">
         <v>129400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>74200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>167300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>110000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>80700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>80100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>157700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>74000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>146500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>112000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>66900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>89400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>186900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>123500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>70200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>90200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>92500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>41100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>28800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>133100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>132600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>122400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>15500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>197300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>159700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>125400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3959,8 +4055,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4016,252 +4112,261 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E45" s="3">
         <v>15900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>52000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>72000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>62100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>30100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>63600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>43800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>271700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>159400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>156600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1393500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>153300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>127500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>141200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>88700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>323300</v>
+      </c>
+      <c r="E46" s="3">
         <v>295600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>299600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>251100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>319300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>297100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>235800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>216900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>250600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>215600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>200800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>149200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>261900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>207900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>220000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>205300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>264100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>218600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>166000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>185200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>202400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>175500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>96100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>128300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1742100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1405200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1335800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1413300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1614600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1515100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1335500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1415700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E47" s="3">
         <v>57300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>53100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>55500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>54200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>53300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4277,8 +4382,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4289,139 +4394,145 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
+      <c r="Z47" s="3">
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC47" s="3">
         <v>62000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>63200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>64300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>84600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>91400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>94300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>265500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>210000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>767700</v>
+      </c>
+      <c r="E48" s="3">
         <v>771500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>779600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>787200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>789400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>792900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>713600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>720700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>723100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>726500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>736300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>743600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>745800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>701800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>710200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>718000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>719700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>723100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>731500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>737300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>739200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>743300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>748900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>758600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>757600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1817400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1818000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1707400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2177700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1317700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1288400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1269700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1253700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4462,7 +4573,7 @@
         <v>330200</v>
       </c>
       <c r="P49" s="3">
-        <v>339600</v>
+        <v>330200</v>
       </c>
       <c r="Q49" s="3">
         <v>339600</v>
@@ -4471,58 +4582,61 @@
         <v>339600</v>
       </c>
       <c r="S49" s="3">
+        <v>339600</v>
+      </c>
+      <c r="T49" s="3">
         <v>339700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>340000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>340300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>340500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>340800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>341100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>341300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>341600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>341900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>643900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>736600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>741600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>527300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>795400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>800900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>806500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>811200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E52" s="3">
         <v>20100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>56900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>43100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>68200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>37300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>59100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>84100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>44700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>44300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>58600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>112600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1973800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>99400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>99900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>51200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>45700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1537700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1509300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1544700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1517400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1473000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1504500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1412400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1373300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1346300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1388500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1368400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1366100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1315000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1363300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1300900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1345900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1302000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1363800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1349400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1327900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1309900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1304400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1292100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1219400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1233800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4309600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4081600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3961600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3763800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3918500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3798500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3728300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3736200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,153 +5230,157 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>41600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>26400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>24800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>31500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E58" s="3">
         <v>73500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>79900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>78200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>76600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>75000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>79900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>79800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>80300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>80400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>80700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>80500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>79700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>73600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>30000</v>
       </c>
       <c r="R58" s="3">
         <v>30000</v>
@@ -5269,8 +5403,8 @@
       <c r="X58" s="3">
         <v>30000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
+      <c r="Y58" s="3">
+        <v>30000</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
@@ -5278,8 +5412,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>4800</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>4800</v>
@@ -5288,426 +5422,441 @@
         <v>4800</v>
       </c>
       <c r="AE58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF58" s="3">
         <v>6000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E59" s="3">
         <v>102000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>249100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>330600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>164200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>267800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>306800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>148700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>116900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>257600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>157100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>132200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>445000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>485800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>397000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>421200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>418800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>398100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>336100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>317000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>347000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>311100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>288000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>862200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>823600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>829000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>826200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>744000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>691300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>742400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>732200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>642400</v>
+      </c>
+      <c r="E60" s="3">
         <v>637800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>641600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>637300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>563500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>617200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>603000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>574700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>522000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>526600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>560400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>553700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>520500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>510600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>483000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>522100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>438300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>454500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>451800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>429800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>368300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>348600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>348100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>312400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>290300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>886700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>870000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>860200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>760000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>780800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>728000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>776100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>765500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1086000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1094300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1108000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1096400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1108100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1115500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1022600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1013600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1025000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1086900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1071000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1104300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1041400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1065500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>405000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>220000</v>
       </c>
       <c r="S61" s="3">
         <v>220000</v>
       </c>
       <c r="T61" s="3">
+        <v>220000</v>
+      </c>
+      <c r="U61" s="3">
         <v>285000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>330000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>355000</v>
       </c>
       <c r="W61" s="3">
         <v>355000</v>
       </c>
       <c r="X61" s="3">
-        <v>380000</v>
+        <v>355000</v>
       </c>
       <c r="Y61" s="3">
         <v>380000</v>
       </c>
       <c r="Z61" s="3">
-        <v>350000</v>
+        <v>380000</v>
       </c>
       <c r="AA61" s="3">
         <v>350000</v>
       </c>
       <c r="AB61" s="3">
+        <v>350000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>380000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>31200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>47400</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>91000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>100400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>100900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>101300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E62" s="3">
         <v>72100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>76600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77300</v>
       </c>
-      <c r="G62" s="3">
-        <v>78100</v>
-      </c>
       <c r="H62" s="3">
+        <v>82200</v>
+      </c>
+      <c r="I62" s="3">
         <v>47300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>48200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>50700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>49100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>799300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>775600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>789000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>802200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>777200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>775300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>788500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>831200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>829100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>796800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>797000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>443600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>435500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>441600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>297400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>265900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>249900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>225600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>238600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1804800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1826800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1811600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1754400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1787900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1685600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1650800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1612600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1682400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1707600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1724600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1652300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1696300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1688600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1519200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1449100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1543500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1561500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1562400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1514200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1562200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1560100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1462200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1440800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1754500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1423200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1436100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1143300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1230500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1170100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1198100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1199700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-129900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-158200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-138200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-137600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-135800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-121600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-122700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-115100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-140600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-178500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-192700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-173900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-164700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-217000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-62400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-62900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-87400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-103200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-78900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-128500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-134000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-93400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-43600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-74900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>43200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-51000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>29000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>102200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>67000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-14600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-295500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-282100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-294200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-281400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-283400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-273100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-277500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-266300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-294000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-339200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-358500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-337200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-333800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-387800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-173400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-147100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-179800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-212100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-234400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-204300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-257700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-268000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-242800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-207000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2555100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2658300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2525500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2620500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2687900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2628400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2536500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>52400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>49600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-182400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-95600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>95400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-79800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>35300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>81600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-32200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7428,16 +7627,16 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>800</v>
       </c>
       <c r="M83" s="3">
         <v>800</v>
       </c>
       <c r="N83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>900</v>
@@ -7446,13 +7645,13 @@
         <v>900</v>
       </c>
       <c r="Q83" s="3">
+        <v>900</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1200</v>
       </c>
       <c r="T83" s="3">
         <v>1200</v>
@@ -7461,49 +7660,52 @@
         <v>1200</v>
       </c>
       <c r="V83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W83" s="3">
         <v>1400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>1600</v>
       </c>
       <c r="Y83" s="3">
         <v>1600</v>
       </c>
       <c r="Z83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>93400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>29000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>119200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>28900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>30200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>29700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E89" s="3">
         <v>57500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-85000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>49700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>61800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>108400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-54100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>37700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>83200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>113800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>43300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-19300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>19000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-32700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-57500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3600</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>145400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-34200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>161300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>68800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>73200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-44700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-400</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-400</v>
       </c>
       <c r="Q91" s="3">
         <v>-400</v>
       </c>
       <c r="R91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-200</v>
       </c>
       <c r="V91" s="3">
         <v>-200</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-362500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-120900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-128300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-188800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-300</v>
       </c>
       <c r="V94" s="3">
         <v>-300</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>-100</v>
       </c>
       <c r="AA94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-514900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-350700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-69700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-74200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-232900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-143900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>78600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-94500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8595,44 +8829,44 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>500</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,109 +9233,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-32500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-55000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-41600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>67800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-55700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-53500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-65100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-71200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-45100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-27700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>30800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-520600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>350600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-16600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9135,8 +9384,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9166,131 +9415,137 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>4700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E102" s="3">
         <v>25700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-95900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>57800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-35900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>40900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-31800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>54100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-64500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1027200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>59600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-134400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-138700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-69500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>150400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-155400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>49100</v>
       </c>
     </row>
